--- a/cplusplus-read-market/app/aes-cotizaciones-historicas.xlsx
+++ b/cplusplus-read-market/app/aes-cotizaciones-historicas.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName function="false" hidden="false" name="HTML_1___tbcotizaciones" vbProcedure="false">AES!$A$1:$H$146</definedName>
     <definedName function="false" hidden="false" name="HTML_all" vbProcedure="false">AES!$A$1:$H$146</definedName>
-    <definedName function="false" hidden="false" name="HTML_tables" vbProcedure="false">#REF!</definedName>
+    <definedName function="false" hidden="false" name="HTML_tables" vbProcedure="false">#ref!</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
